--- a/All_TCB_entries_final.xlsx
+++ b/All_TCB_entries_final.xlsx
@@ -8,18 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\Projects\open_admet\pxr\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36D82CCD-1DA7-4E3E-B77D-91A2E2387629}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FFBCD57-4B51-401E-B21A-866D6565EF76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-6770" yWindow="-21710" windowWidth="38620" windowHeight="21100" xr2:uid="{58A85CA8-C657-4EF2-8863-04CE2E52EE30}"/>
   </bookViews>
   <sheets>
     <sheet name="Updated" sheetId="1" r:id="rId1"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId2"/>
-  </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Updated!$A$5:$J$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Updated!$A$5:$N$29</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -45,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="113">
   <si>
     <t>Position</t>
   </si>
@@ -137,9 +134,6 @@
     <t>OpenFold3</t>
   </si>
   <si>
-    <t>openfold second attempt, using fineslice tuning (~60 cycles)</t>
-  </si>
-  <si>
     <t>2026-05-28 21:53 UTC</t>
   </si>
   <si>
@@ -147,9 +141,6 @@
   </si>
   <si>
     <t>2026-06-23 22:29 UTC</t>
-  </si>
-  <si>
-    <t>openfold - fine slice tuning with short cycles (~30)</t>
   </si>
   <si>
     <t>2026-06-28 00:00 UTC</t>
@@ -261,6 +252,159 @@
   <si>
     <t>LDDT-PLI Difference to My Top score (error is ~0.018)</t>
   </si>
+  <si>
+    <t>run8</t>
+  </si>
+  <si>
+    <t>182/184 scored | mean best 3.10 | median 2.76 | succ@2A 37%</t>
+  </si>
+  <si>
+    <t>Run</t>
+  </si>
+  <si>
+    <t>run9</t>
+  </si>
+  <si>
+    <t>182/184 scored | mean best 3.15 | median 2.61 | succ@2A 40%</t>
+  </si>
+  <si>
+    <t>run10</t>
+  </si>
+  <si>
+    <t>run12</t>
+  </si>
+  <si>
+    <t>182/184 scored | mean best 3.33 | median 3.01 | succ@2A 32%</t>
+  </si>
+  <si>
+    <t>Submission File</t>
+  </si>
+  <si>
+    <t>PXR_structurerack_BSD_07.zip</t>
+  </si>
+  <si>
+    <t>PXR_structuretrack_BSD_03.zip</t>
+  </si>
+  <si>
+    <t>submission_round3.zip</t>
+  </si>
+  <si>
+    <t>PXR_structuretrack_BSD_09.zip</t>
+  </si>
+  <si>
+    <t>PXR_structuretrack_BSD_10.zip</t>
+  </si>
+  <si>
+    <t>PXR_structuretrack_BSD_12_ph4model1.zip</t>
+  </si>
+  <si>
+    <t>PXR_structuretrack_BSD_14_topIPTM_longrun_LDDT0x516.zip</t>
+  </si>
+  <si>
+    <t>PXR_structuretrack_BSD_20_AF3_tune1.zip</t>
+  </si>
+  <si>
+    <t>PXR_structuretrack_BSD_21_AF3_tune2.zip</t>
+  </si>
+  <si>
+    <t>PXR_structuretrack_BSD_22_AF3_tune2B.zip</t>
+  </si>
+  <si>
+    <t>PXR_structuretrack_BSD_23_AF3_tune2C.zip</t>
+  </si>
+  <si>
+    <t>PXR_structuretrack_BSD_24_ptx_clusteredmedian.zip</t>
+  </si>
+  <si>
+    <t>PXR_structuretrack_BSD_25_ptx_clusteredtop.zip</t>
+  </si>
+  <si>
+    <t>PXR_structuretrack_BSD_26_ptx_globaltop.zip</t>
+  </si>
+  <si>
+    <t>PXR_structuretrack_BSD_27_ptxv2_clustertop.zip</t>
+  </si>
+  <si>
+    <t>PXR_structuretrack_BSD_28_ptxv1_notemp_clustertop.zip</t>
+  </si>
+  <si>
+    <t>PXR_structuretrack_BSD_29_ptxv1_notemp_globaltop.zip</t>
+  </si>
+  <si>
+    <t>PXR_structuretrack_BSD_30_ptxv2_notemp_clustertop.zip</t>
+  </si>
+  <si>
+    <t>PXR_structuretrack_BSD_02.zip</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PXR_structuretrack_BSD_08_LDDT0x5267.zip </t>
+  </si>
+  <si>
+    <t>Evaluation full output vs 184</t>
+  </si>
+  <si>
+    <t>Evaluation of submission files only</t>
+  </si>
+  <si>
+    <t>181/184 scored | mean best 4.28 | median 3.99 | succ@2A 20%</t>
+  </si>
+  <si>
+    <t>184/184 scored | mean best 4.15 | median 3.70 | succ@2A 20%</t>
+  </si>
+  <si>
+    <t>184/184 scored | mean best 4.24 | median 3.98 | succ@2A 18%</t>
+  </si>
+  <si>
+    <t>182/184 scored | mean best 4.22 | median 3.98 | succ@2A 18%</t>
+  </si>
+  <si>
+    <t>182/184 scored | mean best 4.23 | median 3.95 | succ@2A 17%</t>
+  </si>
+  <si>
+    <t>184/184 scored | mean best 4.40 | median 3.95 | succ@2A 16%</t>
+  </si>
+  <si>
+    <t>184/184 scored | mean best 4.46 | median 4.15 | succ@2A 18%</t>
+  </si>
+  <si>
+    <t>184/184 scored | mean best 4.38 | median 4.07 | succ@2A 15%</t>
+  </si>
+  <si>
+    <t>184/184 scored | mean best 4.43 | median 4.16 | succ@2A 14%</t>
+  </si>
+  <si>
+    <t>184/184 scored | mean best 5.83 | median 6.26 | succ@2A 3%</t>
+  </si>
+  <si>
+    <t>182/184 scored | mean best 4.22 | median 4.04 | succ@2A 19%</t>
+  </si>
+  <si>
+    <t>184/184 scored | mean best 3.70 | median 3.26 | succ@2A 23%</t>
+  </si>
+  <si>
+    <t>182/184 scored | mean best 4.25 | median 3.89 | succ@2A 14%</t>
+  </si>
+  <si>
+    <t>ckpt_12_52</t>
+  </si>
+  <si>
+    <t>ckpt_3_16</t>
+  </si>
+  <si>
+    <t>ckpt_22_92</t>
+  </si>
+  <si>
+    <t>openfold second attempt, using fineslice tuning (52 cycles)</t>
+  </si>
+  <si>
+    <t>openfold - fine slice tuning with short cycles (16)</t>
+  </si>
+  <si>
+    <t>184/184 scored | mean best 3.08 | median 2.71 | succ@2A 37%</t>
+  </si>
 </sst>
 </file>
 
@@ -269,7 +413,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -336,6 +480,37 @@
     </font>
     <font>
       <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Display"/>
+      <family val="2"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
       <sz val="14"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
@@ -417,7 +592,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -465,7 +640,6 @@
     <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -526,8 +700,55 @@
     <xf numFmtId="2" fontId="6" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="10" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="10" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="10" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="10" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="12" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="11" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="11" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="11" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="11" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="13" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="13" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="13" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="13" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1516,450 +1737,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Full_competition"/>
-      <sheetName val="final_scores_fullset"/>
-      <sheetName val="Updated"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2">
-        <row r="6">
-          <cell r="E6">
-            <v>0.57250000000000001</v>
-          </cell>
-          <cell r="F6">
-            <v>3.4085000000000001</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="E7">
-            <v>0.55569999999999997</v>
-          </cell>
-          <cell r="F7">
-            <v>3.8081</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="E8">
-            <v>0.5464</v>
-          </cell>
-          <cell r="F8">
-            <v>3.8691</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="E9">
-            <v>0.54159999999999997</v>
-          </cell>
-          <cell r="F9">
-            <v>3.6383999999999999</v>
-          </cell>
-        </row>
-        <row r="10">
-          <cell r="E10">
-            <v>0.53639999999999999</v>
-          </cell>
-          <cell r="F10">
-            <v>3.6913</v>
-          </cell>
-        </row>
-        <row r="11">
-          <cell r="E11">
-            <v>0.53469999999999995</v>
-          </cell>
-          <cell r="F11">
-            <v>3.7463000000000002</v>
-          </cell>
-        </row>
-        <row r="12">
-          <cell r="E12">
-            <v>0.5323</v>
-          </cell>
-          <cell r="F12">
-            <v>3.6846000000000001</v>
-          </cell>
-        </row>
-        <row r="13">
-          <cell r="E13">
-            <v>0.53180000000000005</v>
-          </cell>
-          <cell r="F13">
-            <v>3.847</v>
-          </cell>
-        </row>
-        <row r="14">
-          <cell r="E14">
-            <v>0.5302</v>
-          </cell>
-          <cell r="F14">
-            <v>3.7166000000000001</v>
-          </cell>
-        </row>
-        <row r="15">
-          <cell r="E15">
-            <v>0.52669999999999995</v>
-          </cell>
-          <cell r="F15">
-            <v>3.7831000000000001</v>
-          </cell>
-        </row>
-        <row r="16">
-          <cell r="E16">
-            <v>0.52659999999999996</v>
-          </cell>
-          <cell r="F16">
-            <v>4.1870000000000003</v>
-          </cell>
-        </row>
-        <row r="17">
-          <cell r="E17">
-            <v>0.52</v>
-          </cell>
-          <cell r="F17">
-            <v>3.8843999999999999</v>
-          </cell>
-        </row>
-        <row r="18">
-          <cell r="E18">
-            <v>0.51739999999999997</v>
-          </cell>
-          <cell r="F18">
-            <v>3.8852000000000002</v>
-          </cell>
-        </row>
-        <row r="19">
-          <cell r="E19">
-            <v>0.51619999999999999</v>
-          </cell>
-          <cell r="F19">
-            <v>3.9514999999999998</v>
-          </cell>
-        </row>
-        <row r="20">
-          <cell r="E20">
-            <v>0.51580000000000004</v>
-          </cell>
-          <cell r="F20">
-            <v>3.9194</v>
-          </cell>
-        </row>
-        <row r="21">
-          <cell r="E21">
-            <v>0.51390000000000002</v>
-          </cell>
-          <cell r="F21">
-            <v>3.9076</v>
-          </cell>
-        </row>
-        <row r="22">
-          <cell r="E22">
-            <v>0.51060000000000005</v>
-          </cell>
-          <cell r="F22">
-            <v>3.9125999999999999</v>
-          </cell>
-        </row>
-        <row r="23">
-          <cell r="E23">
-            <v>0.51049999999999995</v>
-          </cell>
-          <cell r="F23">
-            <v>3.8502999999999998</v>
-          </cell>
-        </row>
-        <row r="24">
-          <cell r="E24">
-            <v>0.51039999999999996</v>
-          </cell>
-          <cell r="F24">
-            <v>4.6835000000000004</v>
-          </cell>
-        </row>
-        <row r="25">
-          <cell r="E25">
-            <v>0.50800000000000001</v>
-          </cell>
-          <cell r="F25">
-            <v>3.9346999999999999</v>
-          </cell>
-        </row>
-        <row r="26">
-          <cell r="E26">
-            <v>0.50760000000000005</v>
-          </cell>
-          <cell r="F26">
-            <v>3.9864999999999999</v>
-          </cell>
-        </row>
-        <row r="27">
-          <cell r="E27">
-            <v>0.50460000000000005</v>
-          </cell>
-          <cell r="F27">
-            <v>3.9295</v>
-          </cell>
-        </row>
-        <row r="28">
-          <cell r="E28">
-            <v>0.50390000000000001</v>
-          </cell>
-          <cell r="F28">
-            <v>4.0011999999999999</v>
-          </cell>
-        </row>
-        <row r="29">
-          <cell r="E29">
-            <v>0.50149999999999995</v>
-          </cell>
-          <cell r="F29">
-            <v>4.2687999999999997</v>
-          </cell>
-        </row>
-        <row r="30">
-          <cell r="E30">
-            <v>0.49509999999999998</v>
-          </cell>
-          <cell r="F30">
-            <v>4.0656999999999996</v>
-          </cell>
-        </row>
-        <row r="31">
-          <cell r="E31">
-            <v>0.49390000000000001</v>
-          </cell>
-          <cell r="F31">
-            <v>4.0774999999999997</v>
-          </cell>
-        </row>
-        <row r="32">
-          <cell r="E32">
-            <v>0.49030000000000001</v>
-          </cell>
-          <cell r="F32">
-            <v>4.0252999999999997</v>
-          </cell>
-        </row>
-        <row r="33">
-          <cell r="E33">
-            <v>0.48170000000000002</v>
-          </cell>
-          <cell r="F33">
-            <v>4.1261000000000001</v>
-          </cell>
-        </row>
-        <row r="34">
-          <cell r="E34">
-            <v>0.48010000000000003</v>
-          </cell>
-          <cell r="F34">
-            <v>4.1456999999999997</v>
-          </cell>
-        </row>
-        <row r="35">
-          <cell r="E35">
-            <v>0.47739999999999999</v>
-          </cell>
-          <cell r="F35">
-            <v>4.1765999999999996</v>
-          </cell>
-        </row>
-        <row r="36">
-          <cell r="E36">
-            <v>0.47539999999999999</v>
-          </cell>
-          <cell r="F36">
-            <v>4.2713999999999999</v>
-          </cell>
-        </row>
-        <row r="37">
-          <cell r="E37">
-            <v>0.4723</v>
-          </cell>
-          <cell r="F37">
-            <v>4.3452000000000002</v>
-          </cell>
-        </row>
-        <row r="38">
-          <cell r="E38">
-            <v>0.47210000000000002</v>
-          </cell>
-          <cell r="F38">
-            <v>4.2112999999999996</v>
-          </cell>
-        </row>
-        <row r="39">
-          <cell r="E39">
-            <v>0.47120000000000001</v>
-          </cell>
-          <cell r="F39">
-            <v>4.1452</v>
-          </cell>
-        </row>
-        <row r="40">
-          <cell r="E40">
-            <v>0.47110000000000002</v>
-          </cell>
-          <cell r="F40">
-            <v>4.1996000000000002</v>
-          </cell>
-        </row>
-        <row r="41">
-          <cell r="E41">
-            <v>0.4708</v>
-          </cell>
-          <cell r="F41">
-            <v>4.8623000000000003</v>
-          </cell>
-        </row>
-        <row r="42">
-          <cell r="E42">
-            <v>0.46789999999999998</v>
-          </cell>
-          <cell r="F42">
-            <v>4.2403000000000004</v>
-          </cell>
-        </row>
-        <row r="43">
-          <cell r="E43">
-            <v>0.4657</v>
-          </cell>
-          <cell r="F43">
-            <v>4.2161</v>
-          </cell>
-        </row>
-        <row r="44">
-          <cell r="E44">
-            <v>0.46450000000000002</v>
-          </cell>
-          <cell r="F44">
-            <v>4.1875</v>
-          </cell>
-        </row>
-        <row r="45">
-          <cell r="E45">
-            <v>0.46329999999999999</v>
-          </cell>
-          <cell r="F45">
-            <v>4.3178999999999998</v>
-          </cell>
-        </row>
-        <row r="46">
-          <cell r="E46">
-            <v>0.4632</v>
-          </cell>
-          <cell r="F46">
-            <v>4.3108000000000004</v>
-          </cell>
-        </row>
-        <row r="47">
-          <cell r="E47">
-            <v>0.4632</v>
-          </cell>
-          <cell r="F47">
-            <v>4.3108000000000004</v>
-          </cell>
-        </row>
-        <row r="48">
-          <cell r="E48">
-            <v>0.45889999999999997</v>
-          </cell>
-          <cell r="F48">
-            <v>4.3068</v>
-          </cell>
-        </row>
-        <row r="49">
-          <cell r="E49">
-            <v>0.45190000000000002</v>
-          </cell>
-          <cell r="F49">
-            <v>4.2521000000000004</v>
-          </cell>
-        </row>
-        <row r="50">
-          <cell r="E50">
-            <v>0.45179999999999998</v>
-          </cell>
-          <cell r="F50">
-            <v>4.3343999999999996</v>
-          </cell>
-        </row>
-        <row r="51">
-          <cell r="E51">
-            <v>0.41970000000000002</v>
-          </cell>
-          <cell r="F51">
-            <v>4.6117999999999997</v>
-          </cell>
-        </row>
-        <row r="52">
-          <cell r="E52">
-            <v>0.38219999999999998</v>
-          </cell>
-          <cell r="F52">
-            <v>4.9991000000000003</v>
-          </cell>
-        </row>
-        <row r="53">
-          <cell r="E53">
-            <v>0.33350000000000002</v>
-          </cell>
-          <cell r="F53">
-            <v>5.0967000000000002</v>
-          </cell>
-        </row>
-        <row r="54">
-          <cell r="E54">
-            <v>0.31919999999999998</v>
-          </cell>
-          <cell r="F54">
-            <v>5.508</v>
-          </cell>
-        </row>
-        <row r="55">
-          <cell r="E55">
-            <v>0.29320000000000002</v>
-          </cell>
-          <cell r="F55">
-            <v>6.2464000000000004</v>
-          </cell>
-        </row>
-        <row r="56">
-          <cell r="E56">
-            <v>0.17979999999999999</v>
-          </cell>
-          <cell r="F56">
-            <v>7.4055</v>
-          </cell>
-        </row>
-        <row r="57">
-          <cell r="F57">
-            <v>13.2103</v>
-          </cell>
-        </row>
-        <row r="58">
-          <cell r="F58">
-            <v>11.4932</v>
-          </cell>
-        </row>
-        <row r="59">
-          <cell r="F59">
-            <v>20</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -2277,7 +2054,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{516C1556-172C-4D77-91AF-62C41FF4D2EF}">
-  <dimension ref="A2:P28"/>
+  <dimension ref="A2:N28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24.140625" style="1" hidden="1" customWidth="1"/>
@@ -2286,94 +2063,112 @@
     <col min="4" max="4" width="16.42578125" customWidth="1"/>
     <col min="5" max="5" width="16.85546875" customWidth="1"/>
     <col min="6" max="6" width="15.5703125" customWidth="1"/>
-    <col min="7" max="7" width="13.85546875" customWidth="1"/>
-    <col min="8" max="8" width="28" style="2" customWidth="1"/>
+    <col min="7" max="7" width="13.85546875" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="12.7109375" style="2" customWidth="1"/>
     <col min="9" max="9" width="24.28515625" style="2" customWidth="1"/>
-    <col min="10" max="10" width="125.28515625" customWidth="1"/>
+    <col min="10" max="10" width="19" style="2" customWidth="1"/>
+    <col min="11" max="11" width="50" style="2" customWidth="1"/>
+    <col min="12" max="12" width="62.42578125" style="2" customWidth="1"/>
+    <col min="13" max="13" width="68.42578125" style="2" customWidth="1"/>
+    <col min="14" max="14" width="125.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:16" ht="31.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="16" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
-    <row r="3" spans="1:16" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="B3" s="41" t="s">
-        <v>62</v>
+    <row r="3" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="B3" s="39" t="s">
+        <v>60</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="21" t="s">
+      <c r="B5" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="21" t="s">
+      <c r="C5" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="22" t="s">
+      <c r="D5" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="E5" s="21" t="s">
+      <c r="E5" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="F5" s="21" t="s">
+      <c r="F5" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="G5" s="21" t="s">
+      <c r="G5" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="H5" s="22" t="s">
-        <v>63</v>
-      </c>
-      <c r="I5" s="22" t="s">
+      <c r="H5" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="I5" s="21" t="s">
         <v>7</v>
       </c>
       <c r="J5" s="21" t="s">
-        <v>61</v>
+        <v>64</v>
+      </c>
+      <c r="K5" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="L5" s="21" t="s">
+        <v>93</v>
+      </c>
+      <c r="M5" s="21" t="s">
+        <v>92</v>
+      </c>
+      <c r="N5" s="20" t="s">
+        <v>59</v>
       </c>
     </row>
-    <row r="6" spans="1:16" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A6" s="4">
         <v>9</v>
       </c>
-      <c r="B6" s="28" t="s">
+      <c r="B6" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="20" t="s">
+      <c r="C6" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="D6" s="24">
+      <c r="D6" s="23">
         <v>0.52669999999999995</v>
       </c>
-      <c r="E6" s="24">
+      <c r="E6" s="23">
         <v>3.7831000000000001</v>
       </c>
-      <c r="F6" s="24">
+      <c r="F6" s="23">
         <v>0.90039999999999998</v>
       </c>
-      <c r="G6" s="20">
+      <c r="G6" s="19">
         <v>1</v>
       </c>
-      <c r="H6" s="23">
-        <f>D6-D$6</f>
+      <c r="H6" s="22">
+        <f t="shared" ref="H6:H27" si="0">D6-D$6</f>
         <v>0</v>
       </c>
-      <c r="I6" s="32" t="s">
+      <c r="I6" s="31" t="s">
         <v>10</v>
       </c>
-      <c r="J6" s="6" t="s">
+      <c r="J6" s="53"/>
+      <c r="K6" s="46" t="s">
+        <v>91</v>
+      </c>
+      <c r="L6" s="40" t="s">
+        <v>94</v>
+      </c>
+      <c r="M6" s="31"/>
+      <c r="N6" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="K6" s="19"/>
-      <c r="L6" s="19"/>
-      <c r="M6" s="19"/>
-      <c r="N6" s="19"/>
-      <c r="O6" s="19"/>
-      <c r="P6" s="19"/>
     </row>
-    <row r="7" spans="1:16" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A7" s="4">
         <v>10</v>
       </c>
@@ -2383,36 +2178,36 @@
       <c r="C7" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D7" s="25">
+      <c r="D7" s="24">
         <v>0.52</v>
       </c>
-      <c r="E7" s="25">
+      <c r="E7" s="24">
         <v>3.8843999999999999</v>
       </c>
-      <c r="F7" s="25">
+      <c r="F7" s="24">
         <v>0.90269999999999995</v>
       </c>
       <c r="G7" s="5">
         <v>1</v>
       </c>
-      <c r="H7" s="23">
-        <f t="shared" ref="H7:I11" si="0">D7-D$6</f>
+      <c r="H7" s="22">
+        <f t="shared" si="0"/>
         <v>-6.6999999999999282E-3</v>
       </c>
-      <c r="I7" s="33" t="s">
+      <c r="I7" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="J7" s="6" t="s">
+      <c r="J7" s="32"/>
+      <c r="K7" s="46" t="s">
+        <v>74</v>
+      </c>
+      <c r="L7" s="40"/>
+      <c r="M7" s="32"/>
+      <c r="N7" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="K7" s="19"/>
-      <c r="L7" s="19"/>
-      <c r="M7" s="19"/>
-      <c r="N7" s="19"/>
-      <c r="O7" s="19"/>
-      <c r="P7" s="19"/>
     </row>
-    <row r="8" spans="1:16" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A8" s="4">
         <v>11</v>
       </c>
@@ -2422,36 +2217,42 @@
       <c r="C8" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="25">
+      <c r="D8" s="24">
         <v>0.51739999999999997</v>
       </c>
-      <c r="E8" s="25">
+      <c r="E8" s="24">
         <v>3.8852000000000002</v>
       </c>
-      <c r="F8" s="25">
+      <c r="F8" s="24">
         <v>0.90329999999999999</v>
       </c>
       <c r="G8" s="5">
         <v>1</v>
       </c>
-      <c r="H8" s="23">
+      <c r="H8" s="22">
         <f t="shared" si="0"/>
         <v>-9.299999999999975E-3</v>
       </c>
-      <c r="I8" s="33" t="s">
+      <c r="I8" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="J8" s="6" t="s">
+      <c r="J8" s="32" t="s">
+        <v>67</v>
+      </c>
+      <c r="K8" s="46" t="s">
+        <v>86</v>
+      </c>
+      <c r="L8" s="40" t="s">
+        <v>97</v>
+      </c>
+      <c r="M8" s="57" t="s">
+        <v>112</v>
+      </c>
+      <c r="N8" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="K8" s="19"/>
-      <c r="L8" s="19"/>
-      <c r="M8" s="19"/>
-      <c r="N8" s="19"/>
-      <c r="O8" s="19"/>
-      <c r="P8" s="19"/>
     </row>
-    <row r="9" spans="1:16" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A9" s="4">
         <v>12</v>
       </c>
@@ -2461,36 +2262,36 @@
       <c r="C9" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D9" s="25">
+      <c r="D9" s="24">
         <v>0.51619999999999999</v>
       </c>
-      <c r="E9" s="25">
+      <c r="E9" s="24">
         <v>3.9514999999999998</v>
       </c>
-      <c r="F9" s="25">
+      <c r="F9" s="24">
         <v>0.90190000000000003</v>
       </c>
       <c r="G9" s="5">
         <v>1</v>
       </c>
-      <c r="H9" s="23">
+      <c r="H9" s="22">
         <f t="shared" si="0"/>
         <v>-1.0499999999999954E-2</v>
       </c>
-      <c r="I9" s="33" t="s">
+      <c r="I9" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="J9" s="6" t="s">
+      <c r="J9" s="32"/>
+      <c r="K9" s="46" t="s">
+        <v>77</v>
+      </c>
+      <c r="L9" s="40"/>
+      <c r="M9" s="32"/>
+      <c r="N9" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="K9" s="19"/>
-      <c r="L9" s="19"/>
-      <c r="M9" s="19"/>
-      <c r="N9" s="19"/>
-      <c r="O9" s="19"/>
-      <c r="P9" s="19"/>
     </row>
-    <row r="10" spans="1:16" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A10" s="4">
         <v>13</v>
       </c>
@@ -2500,36 +2301,38 @@
       <c r="C10" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D10" s="25">
+      <c r="D10" s="24">
         <v>0.51580000000000004</v>
       </c>
-      <c r="E10" s="25">
+      <c r="E10" s="24">
         <v>3.9194</v>
       </c>
-      <c r="F10" s="25">
+      <c r="F10" s="24">
         <v>0.90549999999999997</v>
       </c>
       <c r="G10" s="5">
         <v>1</v>
       </c>
-      <c r="H10" s="23">
+      <c r="H10" s="22">
         <f t="shared" si="0"/>
         <v>-1.089999999999991E-2</v>
       </c>
-      <c r="I10" s="33" t="s">
+      <c r="I10" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="J10" s="6" t="s">
+      <c r="J10" s="32"/>
+      <c r="K10" s="46" t="s">
+        <v>82</v>
+      </c>
+      <c r="L10" s="40" t="s">
+        <v>104</v>
+      </c>
+      <c r="M10" s="32"/>
+      <c r="N10" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="K10" s="19"/>
-      <c r="L10" s="19"/>
-      <c r="M10" s="19"/>
-      <c r="N10" s="19"/>
-      <c r="O10" s="19"/>
-      <c r="P10" s="19"/>
     </row>
-    <row r="11" spans="1:16" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A11" s="4">
         <v>14</v>
       </c>
@@ -2539,36 +2342,42 @@
       <c r="C11" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D11" s="25">
+      <c r="D11" s="24">
         <v>0.51390000000000002</v>
       </c>
-      <c r="E11" s="25">
+      <c r="E11" s="24">
         <v>3.9076</v>
       </c>
-      <c r="F11" s="25">
+      <c r="F11" s="24">
         <v>0.9032</v>
       </c>
       <c r="G11" s="5">
         <v>1</v>
       </c>
-      <c r="H11" s="23">
+      <c r="H11" s="22">
         <f t="shared" si="0"/>
         <v>-1.2799999999999923E-2</v>
       </c>
-      <c r="I11" s="33" t="s">
+      <c r="I11" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="J11" s="6" t="s">
+      <c r="J11" s="32" t="s">
+        <v>62</v>
+      </c>
+      <c r="K11" s="46" t="s">
+        <v>83</v>
+      </c>
+      <c r="L11" s="40" t="s">
+        <v>98</v>
+      </c>
+      <c r="M11" s="32" t="s">
+        <v>63</v>
+      </c>
+      <c r="N11" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="K11" s="19"/>
-      <c r="L11" s="19"/>
-      <c r="M11" s="19"/>
-      <c r="N11" s="19"/>
-      <c r="O11" s="19"/>
-      <c r="P11" s="19"/>
     </row>
-    <row r="12" spans="1:16" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A12" s="4">
         <v>18</v>
       </c>
@@ -2578,36 +2387,40 @@
       <c r="C12" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="D12" s="25">
+      <c r="D12" s="24">
         <v>0.50800000000000001</v>
       </c>
-      <c r="E12" s="25">
+      <c r="E12" s="24">
         <v>3.9346999999999999</v>
       </c>
-      <c r="F12" s="25">
+      <c r="F12" s="24">
         <v>0.9052</v>
       </c>
       <c r="G12" s="5">
         <v>1</v>
       </c>
-      <c r="H12" s="23">
-        <f t="shared" ref="H12:I13" si="1">D12-D$6</f>
+      <c r="H12" s="22">
+        <f t="shared" si="0"/>
         <v>-1.8699999999999939E-2</v>
       </c>
-      <c r="I12" s="33" t="s">
+      <c r="I12" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="J12" s="6" t="s">
+      <c r="J12" s="32" t="s">
+        <v>67</v>
+      </c>
+      <c r="K12" s="47" t="s">
+        <v>87</v>
+      </c>
+      <c r="L12" s="45"/>
+      <c r="M12" s="57" t="s">
+        <v>112</v>
+      </c>
+      <c r="N12" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="K12" s="19"/>
-      <c r="L12" s="19"/>
-      <c r="M12" s="19"/>
-      <c r="N12" s="19"/>
-      <c r="O12" s="19"/>
-      <c r="P12" s="19"/>
     </row>
-    <row r="13" spans="1:16" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A13" s="4">
         <v>19</v>
       </c>
@@ -2617,36 +2430,36 @@
       <c r="C13" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D13" s="25">
+      <c r="D13" s="24">
         <v>0.50760000000000005</v>
       </c>
-      <c r="E13" s="25">
+      <c r="E13" s="24">
         <v>3.9864999999999999</v>
       </c>
-      <c r="F13" s="25">
+      <c r="F13" s="24">
         <v>0.90249999999999997</v>
       </c>
       <c r="G13" s="5">
         <v>1</v>
       </c>
-      <c r="H13" s="23">
-        <f t="shared" si="1"/>
+      <c r="H13" s="22">
+        <f t="shared" si="0"/>
         <v>-1.9099999999999895E-2</v>
       </c>
-      <c r="I13" s="33" t="s">
+      <c r="I13" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="J13" s="6" t="s">
+      <c r="J13" s="32"/>
+      <c r="K13" s="46" t="s">
+        <v>84</v>
+      </c>
+      <c r="L13" s="40"/>
+      <c r="M13" s="32"/>
+      <c r="N13" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="K13" s="19"/>
-      <c r="L13" s="19"/>
-      <c r="M13" s="19"/>
-      <c r="N13" s="19"/>
-      <c r="O13" s="19"/>
-      <c r="P13" s="19"/>
     </row>
-    <row r="14" spans="1:16" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A14" s="4">
         <v>23</v>
       </c>
@@ -2656,75 +2469,79 @@
       <c r="C14" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D14" s="25">
+      <c r="D14" s="24">
         <v>0.49509999999999998</v>
       </c>
-      <c r="E14" s="25">
+      <c r="E14" s="24">
         <v>4.0656999999999996</v>
       </c>
-      <c r="F14" s="25">
+      <c r="F14" s="24">
         <v>0.90539999999999998</v>
       </c>
       <c r="G14" s="5">
         <v>1</v>
       </c>
-      <c r="H14" s="23">
-        <f t="shared" ref="H14:I18" si="2">D14-D$6</f>
+      <c r="H14" s="22">
+        <f t="shared" si="0"/>
         <v>-3.1599999999999961E-2</v>
       </c>
-      <c r="I14" s="33" t="s">
+      <c r="I14" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="J14" s="6" t="s">
+      <c r="J14" s="32"/>
+      <c r="K14" s="46" t="s">
+        <v>76</v>
+      </c>
+      <c r="L14" s="40"/>
+      <c r="M14" s="32"/>
+      <c r="N14" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="K14" s="19"/>
-      <c r="L14" s="19"/>
-      <c r="M14" s="19"/>
-      <c r="N14" s="19"/>
-      <c r="O14" s="19"/>
-      <c r="P14" s="19"/>
     </row>
-    <row r="15" spans="1:16" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A15" s="4">
         <v>24</v>
       </c>
-      <c r="B15" s="29" t="s">
+      <c r="B15" s="28" t="s">
         <v>8</v>
       </c>
       <c r="C15" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="D15" s="26">
+      <c r="D15" s="25">
         <v>0.49390000000000001</v>
       </c>
-      <c r="E15" s="26">
+      <c r="E15" s="25">
         <v>4.0774999999999997</v>
       </c>
-      <c r="F15" s="26">
+      <c r="F15" s="25">
         <v>0.88390000000000002</v>
       </c>
       <c r="G15" s="7">
         <v>1</v>
       </c>
-      <c r="H15" s="23">
-        <f t="shared" si="2"/>
+      <c r="H15" s="22">
+        <f t="shared" si="0"/>
         <v>-3.279999999999994E-2</v>
       </c>
-      <c r="I15" s="34" t="s">
+      <c r="I15" s="33" t="s">
         <v>29</v>
       </c>
-      <c r="J15" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="K15" s="19"/>
-      <c r="L15" s="19"/>
-      <c r="M15" s="19"/>
-      <c r="N15" s="19"/>
-      <c r="O15" s="19"/>
-      <c r="P15" s="19"/>
+      <c r="J15" s="54" t="s">
+        <v>107</v>
+      </c>
+      <c r="K15" s="48" t="s">
+        <v>79</v>
+      </c>
+      <c r="L15" s="41" t="s">
+        <v>95</v>
+      </c>
+      <c r="M15" s="33"/>
+      <c r="N15" s="8" t="s">
+        <v>110</v>
+      </c>
     </row>
-    <row r="16" spans="1:16" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A16" s="4">
         <v>25</v>
       </c>
@@ -2732,38 +2549,38 @@
         <v>8</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="D16" s="25">
+        <v>30</v>
+      </c>
+      <c r="D16" s="24">
         <v>0.49030000000000001</v>
       </c>
-      <c r="E16" s="25">
+      <c r="E16" s="24">
         <v>4.0252999999999997</v>
       </c>
-      <c r="F16" s="25">
+      <c r="F16" s="24">
         <v>0.89839999999999998</v>
       </c>
       <c r="G16" s="5">
         <v>1</v>
       </c>
-      <c r="H16" s="23">
-        <f t="shared" si="2"/>
+      <c r="H16" s="22">
+        <f t="shared" si="0"/>
         <v>-3.6399999999999932E-2</v>
       </c>
-      <c r="I16" s="33" t="s">
+      <c r="I16" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="J16" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="K16" s="19"/>
-      <c r="L16" s="19"/>
-      <c r="M16" s="19"/>
-      <c r="N16" s="19"/>
-      <c r="O16" s="19"/>
-      <c r="P16" s="19"/>
+      <c r="J16" s="32"/>
+      <c r="K16" s="46" t="s">
+        <v>75</v>
+      </c>
+      <c r="L16" s="40"/>
+      <c r="M16" s="32"/>
+      <c r="N16" s="6" t="s">
+        <v>31</v>
+      </c>
     </row>
-    <row r="17" spans="1:16" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A17" s="4">
         <v>26</v>
       </c>
@@ -2771,38 +2588,40 @@
         <v>8</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="D17" s="25">
+        <v>32</v>
+      </c>
+      <c r="D17" s="24">
         <v>0.48170000000000002</v>
       </c>
-      <c r="E17" s="25">
+      <c r="E17" s="24">
         <v>4.1261000000000001</v>
       </c>
-      <c r="F17" s="25">
+      <c r="F17" s="24">
         <v>0.87639999999999996</v>
       </c>
       <c r="G17" s="5">
         <v>1</v>
       </c>
-      <c r="H17" s="23">
-        <f t="shared" si="2"/>
+      <c r="H17" s="22">
+        <f t="shared" si="0"/>
         <v>-4.4999999999999929E-2</v>
       </c>
-      <c r="I17" s="35" t="s">
+      <c r="I17" s="34" t="s">
         <v>29</v>
       </c>
-      <c r="J17" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="K17" s="19"/>
-      <c r="L17" s="19"/>
-      <c r="M17" s="19"/>
-      <c r="N17" s="19"/>
-      <c r="O17" s="19"/>
-      <c r="P17" s="19"/>
+      <c r="J17" s="34" t="s">
+        <v>108</v>
+      </c>
+      <c r="K17" s="49" t="s">
+        <v>81</v>
+      </c>
+      <c r="L17" s="41"/>
+      <c r="M17" s="34"/>
+      <c r="N17" s="8" t="s">
+        <v>111</v>
+      </c>
     </row>
-    <row r="18" spans="1:16" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A18" s="9">
         <v>26</v>
       </c>
@@ -2810,38 +2629,44 @@
         <v>8</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="D18" s="25">
+        <v>33</v>
+      </c>
+      <c r="D18" s="24">
         <v>0.48010000000000003</v>
       </c>
-      <c r="E18" s="25">
+      <c r="E18" s="24">
         <v>4.1456999999999997</v>
       </c>
-      <c r="F18" s="25">
+      <c r="F18" s="24">
         <v>0.90259999999999996</v>
       </c>
       <c r="G18" s="5">
         <v>1</v>
       </c>
-      <c r="H18" s="23">
-        <f t="shared" si="2"/>
+      <c r="H18" s="22">
+        <f t="shared" si="0"/>
         <v>-4.6599999999999919E-2</v>
       </c>
-      <c r="I18" s="33" t="s">
+      <c r="I18" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="J18" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="K18" s="19"/>
-      <c r="L18" s="19"/>
-      <c r="M18" s="19"/>
-      <c r="N18" s="19"/>
-      <c r="O18" s="19"/>
-      <c r="P18" s="19"/>
+      <c r="J18" s="32" t="s">
+        <v>68</v>
+      </c>
+      <c r="K18" s="46" t="s">
+        <v>88</v>
+      </c>
+      <c r="L18" s="40" t="s">
+        <v>99</v>
+      </c>
+      <c r="M18" s="32" t="s">
+        <v>69</v>
+      </c>
+      <c r="N18" s="6" t="s">
+        <v>34</v>
+      </c>
     </row>
-    <row r="19" spans="1:16" s="10" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:14" s="10" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A19" s="4">
         <v>28</v>
       </c>
@@ -2849,38 +2674,38 @@
         <v>8</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D19" s="25">
+        <v>35</v>
+      </c>
+      <c r="D19" s="24">
         <v>0.47539999999999999</v>
       </c>
-      <c r="E19" s="25">
+      <c r="E19" s="24">
         <v>4.2713999999999999</v>
       </c>
-      <c r="F19" s="25">
+      <c r="F19" s="24">
         <v>0.90529999999999999</v>
       </c>
       <c r="G19" s="5">
         <v>1</v>
       </c>
-      <c r="H19" s="23">
-        <f t="shared" ref="H19:I22" si="3">D19-D$6</f>
+      <c r="H19" s="22">
+        <f t="shared" si="0"/>
         <v>-5.1299999999999957E-2</v>
       </c>
-      <c r="I19" s="35" t="s">
+      <c r="I19" s="34" t="s">
         <v>29</v>
       </c>
-      <c r="J19" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="K19" s="40"/>
-      <c r="L19" s="40"/>
-      <c r="M19" s="40"/>
-      <c r="N19" s="40"/>
-      <c r="O19" s="40"/>
-      <c r="P19" s="40"/>
+      <c r="J19" s="34"/>
+      <c r="K19" s="49" t="s">
+        <v>78</v>
+      </c>
+      <c r="L19" s="41"/>
+      <c r="M19" s="34"/>
+      <c r="N19" s="8" t="s">
+        <v>36</v>
+      </c>
     </row>
-    <row r="20" spans="1:16" s="10" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:14" s="10" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A20" s="4">
         <v>29</v>
       </c>
@@ -2888,38 +2713,42 @@
         <v>8</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="D20" s="25">
+        <v>37</v>
+      </c>
+      <c r="D20" s="24">
         <v>0.4723</v>
       </c>
-      <c r="E20" s="25">
+      <c r="E20" s="24">
         <v>4.3452000000000002</v>
       </c>
-      <c r="F20" s="25">
+      <c r="F20" s="24">
         <v>0.87509999999999999</v>
       </c>
       <c r="G20" s="5">
         <v>0.98909999999999998</v>
       </c>
-      <c r="H20" s="23">
-        <f t="shared" si="3"/>
+      <c r="H20" s="22">
+        <f t="shared" si="0"/>
         <v>-5.4399999999999948E-2</v>
       </c>
-      <c r="I20" s="35" t="s">
+      <c r="I20" s="34" t="s">
         <v>29</v>
       </c>
-      <c r="J20" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="K20" s="40"/>
-      <c r="L20" s="40"/>
-      <c r="M20" s="40"/>
-      <c r="N20" s="40"/>
-      <c r="O20" s="40"/>
-      <c r="P20" s="40"/>
+      <c r="J20" s="34"/>
+      <c r="K20" s="49" t="s">
+        <v>71</v>
+      </c>
+      <c r="L20" s="41" t="s">
+        <v>106</v>
+      </c>
+      <c r="M20" s="34" t="s">
+        <v>105</v>
+      </c>
+      <c r="N20" s="8" t="s">
+        <v>38</v>
+      </c>
     </row>
-    <row r="21" spans="1:16" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A21" s="4">
         <v>30</v>
       </c>
@@ -2927,38 +2756,44 @@
         <v>8</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="D21" s="25">
+        <v>39</v>
+      </c>
+      <c r="D21" s="24">
         <v>0.47210000000000002</v>
       </c>
-      <c r="E21" s="25">
+      <c r="E21" s="24">
         <v>4.2112999999999996</v>
       </c>
-      <c r="F21" s="25">
+      <c r="F21" s="24">
         <v>0.90429999999999999</v>
       </c>
       <c r="G21" s="5">
         <v>1</v>
       </c>
-      <c r="H21" s="23">
-        <f t="shared" si="3"/>
+      <c r="H21" s="22">
+        <f t="shared" si="0"/>
         <v>-5.4599999999999926E-2</v>
       </c>
-      <c r="I21" s="33" t="s">
+      <c r="I21" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="J21" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="K21" s="19"/>
-      <c r="L21" s="19"/>
-      <c r="M21" s="19"/>
-      <c r="N21" s="19"/>
-      <c r="O21" s="19"/>
-      <c r="P21" s="19"/>
+      <c r="J21" s="32" t="s">
+        <v>65</v>
+      </c>
+      <c r="K21" s="46" t="s">
+        <v>85</v>
+      </c>
+      <c r="L21" s="40" t="s">
+        <v>100</v>
+      </c>
+      <c r="M21" s="32" t="s">
+        <v>66</v>
+      </c>
+      <c r="N21" s="6" t="s">
+        <v>40</v>
+      </c>
     </row>
-    <row r="22" spans="1:16" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A22" s="4">
         <v>31</v>
       </c>
@@ -2966,38 +2801,40 @@
         <v>8</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="D22" s="25">
+        <v>41</v>
+      </c>
+      <c r="D22" s="24">
         <v>0.47120000000000001</v>
       </c>
-      <c r="E22" s="25">
+      <c r="E22" s="24">
         <v>4.1452</v>
       </c>
-      <c r="F22" s="25">
+      <c r="F22" s="24">
         <v>0.91459999999999997</v>
       </c>
       <c r="G22" s="5">
         <v>1</v>
       </c>
-      <c r="H22" s="23">
-        <f t="shared" si="3"/>
+      <c r="H22" s="22">
+        <f t="shared" si="0"/>
         <v>-5.5499999999999938E-2</v>
       </c>
-      <c r="I22" s="36" t="s">
-        <v>44</v>
-      </c>
-      <c r="J22" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="K22" s="19"/>
-      <c r="L22" s="19"/>
-      <c r="M22" s="19"/>
-      <c r="N22" s="19"/>
-      <c r="O22" s="19"/>
-      <c r="P22" s="19"/>
+      <c r="I22" s="35" t="s">
+        <v>42</v>
+      </c>
+      <c r="J22" s="55"/>
+      <c r="K22" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="L22" s="42" t="s">
+        <v>101</v>
+      </c>
+      <c r="M22" s="35"/>
+      <c r="N22" s="11" t="s">
+        <v>43</v>
+      </c>
     </row>
-    <row r="23" spans="1:16" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A23" s="4">
         <v>36</v>
       </c>
@@ -3005,38 +2842,40 @@
         <v>8</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="D23" s="25">
+        <v>44</v>
+      </c>
+      <c r="D23" s="24">
         <v>0.46450000000000002</v>
       </c>
-      <c r="E23" s="25">
+      <c r="E23" s="24">
         <v>4.1875</v>
       </c>
-      <c r="F23" s="25">
+      <c r="F23" s="24">
         <v>0.91249999999999998</v>
       </c>
       <c r="G23" s="5">
         <v>1</v>
       </c>
-      <c r="H23" s="23">
-        <f t="shared" ref="H23:I27" si="4">D23-D$6</f>
+      <c r="H23" s="22">
+        <f t="shared" si="0"/>
         <v>-6.2199999999999922E-2</v>
       </c>
-      <c r="I23" s="37" t="s">
-        <v>60</v>
-      </c>
-      <c r="J23" s="18" t="s">
-        <v>47</v>
-      </c>
-      <c r="K23" s="19"/>
-      <c r="L23" s="19"/>
-      <c r="M23" s="19"/>
-      <c r="N23" s="19"/>
-      <c r="O23" s="19"/>
-      <c r="P23" s="19"/>
+      <c r="I23" s="36" t="s">
+        <v>58</v>
+      </c>
+      <c r="J23" s="56"/>
+      <c r="K23" s="51" t="s">
+        <v>73</v>
+      </c>
+      <c r="L23" s="43" t="s">
+        <v>102</v>
+      </c>
+      <c r="M23" s="36"/>
+      <c r="N23" s="18" t="s">
+        <v>45</v>
+      </c>
     </row>
-    <row r="24" spans="1:16" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A24" s="4">
         <v>37</v>
       </c>
@@ -3044,71 +2883,81 @@
         <v>8</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="D24" s="25">
+        <v>46</v>
+      </c>
+      <c r="D24" s="24">
         <v>0.46329999999999999</v>
       </c>
-      <c r="E24" s="25">
+      <c r="E24" s="24">
         <v>4.3178999999999998</v>
       </c>
-      <c r="F24" s="25">
+      <c r="F24" s="24">
         <v>0.8992</v>
       </c>
       <c r="G24" s="5">
         <v>1</v>
       </c>
-      <c r="H24" s="23">
-        <f t="shared" si="4"/>
+      <c r="H24" s="22">
+        <f t="shared" si="0"/>
         <v>-6.3399999999999956E-2</v>
       </c>
-      <c r="I24" s="35" t="s">
+      <c r="I24" s="34" t="s">
         <v>29</v>
       </c>
-      <c r="J24" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="K24" s="19"/>
-      <c r="L24" s="19"/>
-      <c r="M24" s="19"/>
-      <c r="N24" s="19"/>
-      <c r="O24" s="19"/>
-      <c r="P24" s="19"/>
+      <c r="J24" s="34" t="s">
+        <v>109</v>
+      </c>
+      <c r="K24" s="49" t="s">
+        <v>80</v>
+      </c>
+      <c r="L24" s="41" t="s">
+        <v>96</v>
+      </c>
+      <c r="M24" s="34"/>
+      <c r="N24" s="8" t="s">
+        <v>47</v>
+      </c>
     </row>
-    <row r="25" spans="1:16" s="19" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A25" s="4">
         <v>38</v>
       </c>
-      <c r="B25" s="30" t="s">
-        <v>50</v>
+      <c r="B25" s="29" t="s">
+        <v>48</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="D25" s="27">
+        <v>49</v>
+      </c>
+      <c r="D25" s="26">
         <v>0.4632</v>
       </c>
-      <c r="E25" s="27">
+      <c r="E25" s="26">
         <v>4.3108000000000004</v>
       </c>
-      <c r="F25" s="27">
+      <c r="F25" s="26">
         <v>0.91400000000000003</v>
       </c>
       <c r="G25" s="12">
         <v>1</v>
       </c>
-      <c r="H25" s="23">
-        <f t="shared" si="4"/>
+      <c r="H25" s="22">
+        <f t="shared" si="0"/>
         <v>-6.3499999999999945E-2</v>
       </c>
-      <c r="I25" s="38" t="s">
-        <v>44</v>
-      </c>
-      <c r="J25" s="12" t="s">
-        <v>59</v>
+      <c r="I25" s="37" t="s">
+        <v>42</v>
+      </c>
+      <c r="J25" s="37"/>
+      <c r="K25" s="52" t="s">
+        <v>90</v>
+      </c>
+      <c r="L25" s="44"/>
+      <c r="M25" s="37"/>
+      <c r="N25" s="12" t="s">
+        <v>57</v>
       </c>
     </row>
-    <row r="26" spans="1:16" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A26" s="4">
         <v>46</v>
       </c>
@@ -3116,71 +2965,79 @@
         <v>8</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="D26" s="25">
+        <v>50</v>
+      </c>
+      <c r="D26" s="24">
         <v>0.31919999999999998</v>
       </c>
-      <c r="E26" s="25">
+      <c r="E26" s="24">
         <v>5.508</v>
       </c>
-      <c r="F26" s="25">
+      <c r="F26" s="24">
         <v>0.86960000000000004</v>
       </c>
       <c r="G26" s="5">
         <v>1</v>
       </c>
-      <c r="H26" s="23">
-        <f>D26-D$6</f>
+      <c r="H26" s="22">
+        <f t="shared" si="0"/>
         <v>-0.20749999999999996</v>
       </c>
-      <c r="I26" s="39" t="s">
-        <v>60</v>
-      </c>
-      <c r="J26" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="K26" s="19"/>
-      <c r="L26" s="19"/>
-      <c r="M26" s="19"/>
-      <c r="N26" s="19"/>
-      <c r="O26" s="19"/>
-      <c r="P26" s="19"/>
+      <c r="I26" s="38" t="s">
+        <v>58</v>
+      </c>
+      <c r="J26" s="38"/>
+      <c r="K26" s="51" t="s">
+        <v>89</v>
+      </c>
+      <c r="L26" s="43" t="s">
+        <v>103</v>
+      </c>
+      <c r="M26" s="38"/>
+      <c r="N26" s="18" t="s">
+        <v>51</v>
+      </c>
     </row>
-    <row r="27" spans="1:16" s="19" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A27" s="4">
         <v>48</v>
       </c>
-      <c r="B27" s="31" t="s">
-        <v>54</v>
+      <c r="B27" s="30" t="s">
+        <v>52</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="D27" s="27">
+        <v>53</v>
+      </c>
+      <c r="D27" s="26">
         <v>0.17979999999999999</v>
       </c>
-      <c r="E27" s="27">
+      <c r="E27" s="26">
         <v>7.4055</v>
       </c>
-      <c r="F27" s="27">
+      <c r="F27" s="26">
         <v>0.86799999999999999</v>
       </c>
       <c r="G27" s="12">
         <v>1</v>
       </c>
-      <c r="H27" s="23">
-        <f t="shared" si="4"/>
+      <c r="H27" s="22">
+        <f t="shared" si="0"/>
         <v>-0.34689999999999999</v>
       </c>
-      <c r="I27" s="38" t="s">
+      <c r="I27" s="37" t="s">
+        <v>54</v>
+      </c>
+      <c r="J27" s="37"/>
+      <c r="K27" s="52" t="s">
+        <v>90</v>
+      </c>
+      <c r="L27" s="44"/>
+      <c r="M27" s="37"/>
+      <c r="N27" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="J27" s="17" t="s">
-        <v>58</v>
-      </c>
     </row>
-    <row r="28" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" s="13"/>
       <c r="B28" s="14"/>
       <c r="C28" s="14"/>
@@ -3188,11 +3045,11 @@
       <c r="E28" s="14"/>
       <c r="F28" s="14"/>
       <c r="G28" s="14"/>
-      <c r="J28" s="14"/>
+      <c r="N28" s="14"/>
     </row>
   </sheetData>
-  <autoFilter ref="A5:J29" xr:uid="{FE916E80-99BE-4E2B-8782-7EF96CB311D2}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A6:J29">
+  <autoFilter ref="A5:N29" xr:uid="{FE916E80-99BE-4E2B-8782-7EF96CB311D2}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A6:N29">
       <sortCondition descending="1" ref="D5:D29"/>
     </sortState>
   </autoFilter>
